--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2574,6 +2574,133 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125262304</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brudmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>561795</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6626184</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -2581,11 +2581,6 @@
       <c r="B17" t="n">
         <v>8447</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17010077</v>
+        <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560275.8325303141</v>
+        <v>561586</v>
       </c>
       <c r="R2" t="n">
-        <v>6626431.446225133</v>
+        <v>6626148</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-01-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-01-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,39 +763,48 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Klen senvuxen granlåga, på undersidan</t>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73168344</v>
+        <v>17010077</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
+        <v>89356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560244.1154263464</v>
+        <v>560275.8325303141</v>
       </c>
       <c r="R3" t="n">
-        <v>6626458.134893872</v>
+        <v>6626431.446225133</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +873,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2015-01-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -882,7 +883,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2015-01-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -902,7 +903,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Klen senvuxen granlåga, på undersidan</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -920,7 +926,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73168318</v>
+        <v>73168344</v>
       </c>
       <c r="B4" t="n">
         <v>90676</v>
@@ -962,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560276.8069365214</v>
+        <v>560244.1154263464</v>
       </c>
       <c r="R4" t="n">
-        <v>6626495.940354445</v>
+        <v>6626458.134893872</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73168294</v>
+        <v>73168318</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
+        <v>90676</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,25 +1058,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1082,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560315.0656916351</v>
+        <v>560276.8069365214</v>
       </c>
       <c r="R5" t="n">
-        <v>6626470.365664247</v>
+        <v>6626495.940354445</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,11 +1149,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrblandskog, inslag av hällmarker</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1165,64 +1166,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63965832</v>
+        <v>73168294</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
+        <v>89356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560981.8650361493</v>
+        <v>560315.0656916351</v>
       </c>
       <c r="R6" t="n">
-        <v>6626056.046608747</v>
+        <v>6626470.365664247</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,22 +1238,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,28 +1262,39 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>175970</v>
+        <v>63965832</v>
       </c>
       <c r="B7" t="n">
-        <v>104643</v>
+        <v>56540</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,37 +1307,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>245</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Liarsbo, Ramnäs sn, Vstm</t>
+          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560652.3964889366</v>
+        <v>560981.8650361493</v>
       </c>
       <c r="R7" t="n">
-        <v>6626361.49478831</v>
+        <v>6626056.046608747</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,22 +1372,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-07-24</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-07-24</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,31 +1398,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Vägkant utefter grusväg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73168237</v>
+        <v>175970</v>
       </c>
       <c r="B8" t="n">
-        <v>95522</v>
+        <v>104643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,20 +1426,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,20 +1448,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Liarsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560501.9114214438</v>
+        <v>560652.3964889366</v>
       </c>
       <c r="R8" t="n">
-        <v>6626399.346754943</v>
+        <v>6626361.49478831</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1484,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2011-07-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1489,7 +1494,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2011-07-24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1503,38 +1508,37 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Vägkant utefter grusväg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>78789562</v>
+        <v>73168237</v>
       </c>
       <c r="B9" t="n">
-        <v>96254</v>
+        <v>95522</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1543,26 +1547,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1571,13 +1575,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560550.4736689391</v>
+        <v>560501.9114214438</v>
       </c>
       <c r="R9" t="n">
-        <v>6626454.036639952</v>
+        <v>6626399.346754943</v>
       </c>
       <c r="S9" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1611,7 +1615,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1631,7 +1635,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Blandskog invid skogsbäck</t>
+          <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1649,10 +1653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78789613</v>
+        <v>78789562</v>
       </c>
       <c r="B10" t="n">
-        <v>106964</v>
+        <v>96254</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,40 +1665,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1751,11 +1743,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal vinterväg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,14 +1775,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78789447</v>
+        <v>78789613</v>
       </c>
       <c r="B11" t="n">
-        <v>91623</v>
+        <v>106964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,26 +1791,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560543</v>
+        <v>560550.4736689391</v>
       </c>
       <c r="R11" t="n">
-        <v>6626443</v>
+        <v>6626454.036639952</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,9 +1864,24 @@
           <t>2019-07-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-07-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal vinterväg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,12 +1896,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granskog, inslag av tall, björk</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>I mossa, glest med blåbärsris som följeart</t>
+          <t>Blandskog invid skogsbäck</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1904,69 +1914,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117962945</v>
+        <v>78789447</v>
       </c>
       <c r="B12" t="n">
-        <v>97880</v>
+        <v>91623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>4368</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Usträngsbo, Ramnäs sn, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560300</v>
+        <v>560543</v>
       </c>
       <c r="R12" t="n">
-        <v>6626366</v>
+        <v>6626443</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1990,27 +1987,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2019-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
+          <t>2019-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,80 +2005,94 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Granskog, inslag av tall, björk</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>I mossa, glest med blåbärsris som följeart</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122671099</v>
+        <v>117962945</v>
       </c>
       <c r="B13" t="n">
-        <v>56683</v>
+        <v>97880</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbrobäcken, Ramnäs sn, Vstm</t>
+          <t>Usträngsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560565</v>
+        <v>560300</v>
       </c>
       <c r="R13" t="n">
-        <v>6626352</v>
+        <v>6626366</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2120,27 +2116,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Skrämdes från träd. Sedan tidigare känd järpelokal.</t>
+          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,28 +2145,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Mikael Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Mikael Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122670754</v>
+        <v>122671099</v>
       </c>
       <c r="B14" t="n">
-        <v>56691</v>
+        <v>56683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2179,25 +2176,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2206,11 +2203,7 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2219,14 +2212,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
+          <t>Stenbrobäcken, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560320</v>
+        <v>560565</v>
       </c>
       <c r="R14" t="n">
-        <v>6626329</v>
+        <v>6626352</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2258,7 +2251,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2268,12 +2261,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Plockat grus på vägkanten och i rotvälta</t>
+          <t>Skrämdes från träd. Sedan tidigare känd järpelokal.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,62 +2293,69 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1754224</v>
+        <v>122670754</v>
       </c>
       <c r="B15" t="n">
-        <v>90676</v>
+        <v>56691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Liarsbo 1 km NO, Vstm</t>
+          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562345.7615864609</v>
+        <v>560320</v>
       </c>
       <c r="R15" t="n">
-        <v>6626037.821326988</v>
+        <v>6626329</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2379,27 +2379,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
+          <t>Plockat grus på vägkanten och i rotvälta</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,98 +2410,69 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Tallhällmark 61-90</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>4 substratenheter # Morän</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Niclas Bergius</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115730289</v>
+        <v>127436297</v>
       </c>
       <c r="B16" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>5177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562132</v>
+        <v>560125</v>
       </c>
       <c r="R16" t="n">
-        <v>6625955</v>
+        <v>6626323</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2525,27 +2496,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2556,77 +2512,93 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stående gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125262304</v>
+        <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brudmossen, Ramnäs, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561795</v>
+        <v>560450</v>
       </c>
       <c r="R17" t="n">
-        <v>6626184</v>
+        <v>6626459</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,22 +2622,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2674,27 +2636,1704 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Hällmarksbarrskog</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127436294</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91497</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>560315</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6626440</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Klen granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127436295</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>560232</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6626384</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127436284</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91497</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>561151</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6626222</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127436286</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91497</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>560481</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6626348</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127436299</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>560198</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6626344</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127436303</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>560214</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6626234</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127436291</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>560451</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6626509</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127436287</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>560475</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6626316</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127436289</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105732</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>560581</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6626354</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127436302</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>560192</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6626228</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127436279</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>561085</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6626170</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1754224</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90676</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora Liarsbo 1 km NO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>562345.7615864609</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6626037.821326988</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Tallhällmark 61-90</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>4 substratenheter # Morän</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Niclas Bergius</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115730289</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57414</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562132</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6625955</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bengt Eriksson, Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125262304</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Brudmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>561795</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6626184</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>127436286</v>
       </c>
       <c r="B21" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3148,38 +3148,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3188,10 +3192,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3255,42 +3259,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91533</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3476,7 +3476,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3706,50 +3706,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3795,7 +3799,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3813,54 +3832,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91533</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3906,22 +3921,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3048,31 +3048,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3081,10 +3077,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3148,32 +3144,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3192,10 +3188,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3259,38 +3255,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3476,7 +3476,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3144,32 +3144,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91506</v>
+        <v>91542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3255,32 +3255,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B23" t="n">
-        <v>91542</v>
+        <v>91506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R23" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3037,38 +3037,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3077,10 +3081,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3144,32 +3148,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91542</v>
+        <v>91506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3188,10 +3192,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3255,10 +3259,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91506</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,31 +3270,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3037,42 +3037,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3081,10 +3077,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3148,32 +3144,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91506</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3192,10 +3188,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3259,10 +3255,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436286</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3270,27 +3266,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560481</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626348</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3476,7 +3476,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3706,54 +3706,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R27" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3799,22 +3795,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3832,50 +3813,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R28" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3921,7 +3906,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3037,38 +3037,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3077,10 +3081,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3144,42 +3148,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3037,42 +3037,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3081,10 +3077,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3148,38 +3144,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>127436286</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3706,50 +3706,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91543</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3795,7 +3799,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3813,54 +3832,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3906,22 +3921,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3037,38 +3037,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91543</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3077,10 +3081,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3144,32 +3148,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91543</v>
+        <v>91507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3188,10 +3192,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3255,10 +3259,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91507</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,31 +3270,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3037,32 +3037,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B21" t="n">
-        <v>91543</v>
+        <v>91509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3148,32 +3148,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91507</v>
+        <v>91545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3476,7 +3476,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,11 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2544,14 +2548,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2670,14 +2678,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2796,14 +2808,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2922,14 +2938,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3033,14 +3053,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91509</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3048,31 +3072,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3081,10 +3101,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3144,14 +3164,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3255,14 +3279,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436286</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3270,27 +3298,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3299,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560481</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626348</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3362,7 +3394,11 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3469,14 +3505,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3595,14 +3635,18 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3702,58 +3746,58 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B27" t="n">
-        <v>91545</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R27" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3799,22 +3843,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3828,54 +3857,62 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R28" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3921,7 +3958,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3935,7 +3987,11 @@
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3061,38 +3061,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91550</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3101,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3172,32 +3176,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91549</v>
+        <v>91514</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3216,10 +3220,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3287,10 +3291,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91513</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,31 +3302,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,50 +3754,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,7 +3847,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3865,54 +3884,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91549</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3958,22 +3973,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3754,54 +3754,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B27" t="n">
-        <v>91550</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R27" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3847,22 +3843,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3884,50 +3865,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91550</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R28" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3973,7 +3958,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3061,42 +3061,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91550</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3105,10 +3101,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,32 +3172,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91514</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3220,10 +3216,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3291,10 +3287,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436286</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3302,27 +3298,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560481</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626348</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3061,38 +3061,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3101,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3172,32 +3176,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3216,10 +3220,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3287,10 +3291,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,31 +3302,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3754,50 +3754,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,7 +3847,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3865,54 +3884,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3958,22 +3973,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3061,42 +3061,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3105,10 +3101,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,32 +3172,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91517</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3220,10 +3216,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3291,10 +3287,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436286</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3302,27 +3298,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560481</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626348</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3061,38 +3061,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3101,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3172,32 +3176,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3216,10 +3220,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3287,10 +3291,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,31 +3302,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3754,54 +3754,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R27" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3847,22 +3843,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3884,50 +3865,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R28" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3973,7 +3958,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3061,32 +3061,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,32 +3176,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>91517</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3061,32 +3061,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436286</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>91517</v>
+        <v>91581</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560481</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626348</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,32 +3176,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>91545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,50 +3754,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91581</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,7 +3847,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3865,54 +3884,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3958,22 +3973,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3061,32 +3061,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B21" t="n">
-        <v>91587</v>
+        <v>91552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,10 +3176,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B22" t="n">
-        <v>91551</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3187,31 +3187,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3220,10 +3216,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3291,38 +3287,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,54 +3754,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B27" t="n">
-        <v>91587</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R27" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3847,22 +3843,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3884,50 +3865,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R28" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3973,7 +3958,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3754,50 +3754,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,7 +3847,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3865,54 +3884,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91588</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3958,22 +3973,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>127436286</v>
       </c>
       <c r="B21" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3176,38 +3176,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3216,10 +3220,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R22" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3287,42 +3291,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91588</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3061,10 +3061,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436286</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91557</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3072,31 +3072,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3105,10 +3101,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560481</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626348</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,32 +3172,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436303</v>
+        <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>91557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3220,10 +3216,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560214</v>
+        <v>560481</v>
       </c>
       <c r="R22" t="n">
-        <v>6626234</v>
+        <v>6626348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3291,38 +3287,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3754,54 +3754,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B27" t="n">
-        <v>91593</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R27" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3847,22 +3843,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3884,50 +3865,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R28" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3973,7 +3958,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3061,38 +3061,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3101,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3287,42 +3291,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3754,50 +3754,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,7 +3847,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3865,54 +3884,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91593</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3958,22 +3973,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>127436292</v>
       </c>
       <c r="B17" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127436294</v>
       </c>
       <c r="B18" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127436295</v>
       </c>
       <c r="B19" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>127436284</v>
       </c>
       <c r="B20" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3061,42 +3061,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B21" t="n">
-        <v>91597</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3105,10 +3101,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3179,7 +3175,7 @@
         <v>127436286</v>
       </c>
       <c r="B22" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3291,38 +3287,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>127436287</v>
       </c>
       <c r="B25" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3754,54 +3754,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R27" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3847,22 +3843,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3884,50 +3865,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R28" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3973,7 +3958,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -3061,38 +3061,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436299</v>
+        <v>127436303</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3101,10 +3105,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560198</v>
+        <v>560214</v>
       </c>
       <c r="R21" t="n">
-        <v>6626344</v>
+        <v>6626234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3287,42 +3291,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436303</v>
+        <v>127436299</v>
       </c>
       <c r="B23" t="n">
-        <v>91599</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560214</v>
+        <v>560198</v>
       </c>
       <c r="R23" t="n">
-        <v>6626234</v>
+        <v>6626344</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3646,7 +3646,7 @@
         <v>127436289</v>
       </c>
       <c r="B26" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3754,50 +3754,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>127436279</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>561085</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626170</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,7 +3847,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3865,54 +3884,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>127436302</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560192</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626228</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3958,22 +3973,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127436282</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17010077</v>
+        <v>125286010</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,39 +816,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Brudmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560275.8325303141</v>
+        <v>561698</v>
       </c>
       <c r="R3" t="n">
-        <v>6626431.446225133</v>
+        <v>6626167</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +878,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-01-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-01-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spillning från hona och badgrop</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,44 +897,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Klen senvuxen granlåga, på undersidan</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bertil Svensson, Pia Hagfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73168344</v>
+        <v>175970</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,36 +926,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Liarsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560244.1154263464</v>
+        <v>560652</v>
       </c>
       <c r="R4" t="n">
-        <v>6626458.134893872</v>
+        <v>6626361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,22 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,39 +994,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Vägkant utefter grusväg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73168318</v>
+        <v>127436279</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,36 +1028,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560276.8069365214</v>
+        <v>561085</v>
       </c>
       <c r="R5" t="n">
-        <v>6626495.940354445</v>
+        <v>6626170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,22 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,76 +1105,96 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Gammal barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73168294</v>
+        <v>127436287</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560315.0656916351</v>
+        <v>560475</v>
       </c>
       <c r="R6" t="n">
-        <v>6626470.365664247</v>
+        <v>6626316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,22 +1221,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,44 +1235,52 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63965832</v>
+        <v>127436288</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,21 +1288,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,26 +1310,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560981.8650361493</v>
+        <v>560435</v>
       </c>
       <c r="R7" t="n">
-        <v>6626056.046608747</v>
+        <v>6626288</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,22 +1351,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,31 +1367,50 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>175970</v>
+        <v>127436303</v>
       </c>
       <c r="B8" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,34 +1418,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>245</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Liarsbo, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560652.3964889366</v>
+        <v>560214</v>
       </c>
       <c r="R8" t="n">
-        <v>6626361.49478831</v>
+        <v>6626234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,22 +1481,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-07-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,72 +1500,69 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Vägkant utefter grusväg</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73168237</v>
+        <v>73168257</v>
       </c>
       <c r="B9" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>4404</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560501.9114214438</v>
+        <v>560373</v>
       </c>
       <c r="R9" t="n">
-        <v>6626399.346754943</v>
+        <v>6626309</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1612,19 +1592,9 @@
           <t>2018-09-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,15 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78789562</v>
+        <v>127436284</v>
       </c>
       <c r="B10" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,41 +1638,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Brudmossen, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560550.4736689391</v>
+        <v>561151</v>
       </c>
       <c r="R10" t="n">
-        <v>6626454.036639952</v>
+        <v>6626222</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,22 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,93 +1715,84 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Blandskog invid skogsbäck</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78789613</v>
+        <v>127436286</v>
       </c>
       <c r="B11" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560550.4736689391</v>
+        <v>560481</v>
       </c>
       <c r="R11" t="n">
-        <v>6626454.036639952</v>
+        <v>6626348</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1865,27 +1816,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal vinterväg</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,77 +1830,88 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Blandskog invid skogsbäck</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>78789447</v>
+        <v>122670754</v>
       </c>
       <c r="B12" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560543</v>
+        <v>560320</v>
       </c>
       <c r="R12" t="n">
-        <v>6626443</v>
+        <v>6626329</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1991,12 +1938,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-07-06</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Plockat grus på vägkanten och i rotvälta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,44 +1967,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Granskog, inslag av tall, björk</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>I mossa, glest med blåbärsris som följeart</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117962945</v>
+        <v>127436297</v>
       </c>
       <c r="B13" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,53 +1996,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Usträngsbo, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560300</v>
+        <v>560125</v>
       </c>
       <c r="R13" t="n">
-        <v>6626366</v>
+        <v>6626323</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2120,27 +2055,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,38 +2069,56 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stående gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>122671099</v>
       </c>
       <c r="B14" t="n">
-        <v>56683</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2297,15 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122670754</v>
+        <v>63965825</v>
       </c>
       <c r="B15" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2313,53 +2246,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
+          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560320</v>
+        <v>560982</v>
       </c>
       <c r="R15" t="n">
-        <v>6626329</v>
+        <v>6626056</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2383,27 +2311,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Plockat grus på vägkanten och i rotvälta</t>
+          <t>Meståg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2418,65 +2346,71 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127436297</v>
+        <v>63965832</v>
       </c>
       <c r="B16" t="n">
-        <v>5177</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560125</v>
+        <v>560982</v>
       </c>
       <c r="R16" t="n">
-        <v>6626323</v>
+        <v>6626056</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2500,12 +2434,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2017-02-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2017-02-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2516,50 +2460,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stående gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127436292</v>
+        <v>112973777</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2567,46 +2487,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Lilla Liarsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560450</v>
+        <v>560865</v>
       </c>
       <c r="R17" t="n">
-        <v>6626459</v>
+        <v>6626044</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2630,12 +2553,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökte i björkar. Lockade</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2646,50 +2584,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127436294</v>
+        <v>127436302</v>
       </c>
       <c r="B18" t="n">
-        <v>91563</v>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,31 +2611,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2730,10 +2640,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560315</v>
+        <v>560192</v>
       </c>
       <c r="R18" t="n">
-        <v>6626440</v>
+        <v>6626228</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2780,21 +2690,6 @@
       <c r="AI18" t="inlineStr">
         <is>
           <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Klen granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2816,42 +2711,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127436295</v>
+        <v>127436299</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2860,10 +2751,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560232</v>
+        <v>560198</v>
       </c>
       <c r="R19" t="n">
-        <v>6626384</v>
+        <v>6626344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2910,21 +2801,6 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2946,10 +2822,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127436284</v>
+        <v>117962945</v>
       </c>
       <c r="B20" t="n">
-        <v>91563</v>
+        <v>99153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,46 +2833,53 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Usträngsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561151</v>
+        <v>560300</v>
       </c>
       <c r="R20" t="n">
-        <v>6626222</v>
+        <v>6626366</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3020,12 +2903,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3034,69 +2932,57 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre barrskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Mikael Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127436303</v>
+        <v>127436289</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
+        <v>106243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3105,10 +2991,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560214</v>
+        <v>560581</v>
       </c>
       <c r="R21" t="n">
-        <v>6626234</v>
+        <v>6626354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3176,32 +3062,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127436286</v>
+        <v>127436292</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3220,10 +3106,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560481</v>
+        <v>560450</v>
       </c>
       <c r="R22" t="n">
-        <v>6626348</v>
+        <v>6626459</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3270,6 +3156,21 @@
       <c r="AI22" t="inlineStr">
         <is>
           <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3291,38 +3192,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436299</v>
+        <v>127436295</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3331,10 +3236,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560198</v>
+        <v>560232</v>
       </c>
       <c r="R23" t="n">
-        <v>6626344</v>
+        <v>6626384</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3381,6 +3286,21 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3402,50 +3322,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127436291</v>
+        <v>78789447</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>93215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560451</v>
+        <v>560543</v>
       </c>
       <c r="R24" t="n">
-        <v>6626509</v>
+        <v>6626443</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3472,12 +3390,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2019-07-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2019-07-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3486,37 +3404,39 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Granskog, inslag av tall, björk</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>I mossa, glest med blåbärsris som följeart</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127436287</v>
+        <v>73168242</v>
       </c>
       <c r="B25" t="n">
-        <v>91599</v>
+        <v>89138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3524,43 +3444,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>4404</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560475</v>
+        <v>560463</v>
       </c>
       <c r="R25" t="n">
-        <v>6626316</v>
+        <v>6626416</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3587,12 +3500,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3601,92 +3514,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127436289</v>
+        <v>73168331</v>
       </c>
       <c r="B26" t="n">
-        <v>105856</v>
+        <v>89138</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>4404</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560581</v>
+        <v>560249</v>
       </c>
       <c r="R26" t="n">
-        <v>6626354</v>
+        <v>6626482</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3713,12 +3605,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3727,37 +3619,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127436302</v>
+        <v>17010077</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,42 +3654,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560192</v>
+        <v>560276</v>
       </c>
       <c r="R27" t="n">
-        <v>6626228</v>
+        <v>6626431</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3824,12 +3710,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2015-01-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2015-01-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3838,81 +3724,76 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Klen senvuxen granlåga, på undersidan</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127436279</v>
+        <v>73168294</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brudmossen, Usträngsbo, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561085</v>
+        <v>560315</v>
       </c>
       <c r="R28" t="n">
-        <v>6626170</v>
+        <v>6626470</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3939,12 +3820,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3953,104 +3834,86 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Granlåga # Picea abies</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1754224</v>
+        <v>127436294</v>
       </c>
       <c r="B29" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Liarsbo 1 km NO, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562345.7615864609</v>
+        <v>560315</v>
       </c>
       <c r="R29" t="n">
-        <v>6626037.821326988</v>
+        <v>6626440</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4074,27 +3937,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4108,41 +3956,47 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Tallhällmark 61-90</t>
-        </is>
-      </c>
-      <c r="AN29" t="n">
-        <v>4</v>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>4 substratenheter # Morän</t>
+          <t>Klen granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Niclas Bergius</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115730289</v>
+        <v>73168318</v>
       </c>
       <c r="B30" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4150,53 +4004,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562132</v>
+        <v>560277</v>
       </c>
       <c r="R30" t="n">
-        <v>6625955</v>
+        <v>6626496</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4220,27 +4060,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4249,79 +4074,74 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125262304</v>
+        <v>73168344</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brudmossen, Ramnäs, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561795</v>
+        <v>560244</v>
       </c>
       <c r="R31" t="n">
-        <v>6626184</v>
+        <v>6626458</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4345,22 +4165,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4373,23 +4183,992 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Hällmarksbarrskog</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125529268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stenbrobäcken, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>560588</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6626447</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skrämdes upp</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127436291</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Altarberget, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>560451</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6626509</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>73168237</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stenbromossen SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>560502</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6626399</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2018-09-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2018-09-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1754023</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Liarsbo 1 km  NO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>562234</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6626125</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Antal substrat motsvarar antal mycel, Småkuperat hällmarksområde m fuktiga partier</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Tallhällmark 90+</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>3 substratenheter # Morän</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Niclas Bergius</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1754224</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora Liarsbo 1 km NO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>562346</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6626038</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Tallhällmark 61-90</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>4 substratenheter # Morän</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Niclas Bergius</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130130734</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>562200</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6625910</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>115730289</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562132</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6625955</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125262304</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Brudmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>561795</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6626184</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2788,47 +2788,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73168318</v>
+        <v>135426956</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
+        <v>91937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Altarberget, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560277</v>
+        <v>560118</v>
       </c>
       <c r="R20" t="n">
-        <v>6626496</v>
+        <v>6626316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2855,12 +2856,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,6 +2877,11 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2893,7 +2899,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>73168344</v>
+        <v>73168318</v>
       </c>
       <c r="B21" t="n">
         <v>93235</v>
@@ -2930,10 +2936,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560244</v>
+        <v>560277</v>
       </c>
       <c r="R21" t="n">
-        <v>6626458</v>
+        <v>6626496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2998,61 +3004,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122670754</v>
+        <v>73168344</v>
       </c>
       <c r="B22" t="n">
-        <v>57141</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560320</v>
+        <v>560244</v>
       </c>
       <c r="R22" t="n">
-        <v>6626329</v>
+        <v>6626458</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3079,27 +3071,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Plockat grus på vägkanten och i rotvälta</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3108,28 +3085,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436297</v>
+        <v>122670754</v>
       </c>
       <c r="B23" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,39 +3120,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560125</v>
+        <v>560320</v>
       </c>
       <c r="R23" t="n">
-        <v>6626323</v>
+        <v>6626329</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,12 +3190,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Plockat grus på vägkanten och i rotvälta</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,50 +3221,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stående gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122671099</v>
+        <v>127436297</v>
       </c>
       <c r="B24" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,46 +3248,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenbrobäcken, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560565</v>
+        <v>560125</v>
       </c>
       <c r="R24" t="n">
-        <v>6626352</v>
+        <v>6626323</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3329,27 +3307,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Skrämdes från träd. Sedan tidigare känd järpelokal.</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3360,23 +3323,47 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stående gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125529268</v>
+        <v>122671099</v>
       </c>
       <c r="B25" t="n">
         <v>57132</v>
@@ -3406,14 +3393,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3423,10 +3410,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560588</v>
+        <v>560565</v>
       </c>
       <c r="R25" t="n">
-        <v>6626447</v>
+        <v>6626352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3453,27 +3440,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Skrämdes upp</t>
+          <t>Skrämdes från träd. Sedan tidigare känd järpelokal.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3500,10 +3487,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>63965825</v>
+        <v>125529268</v>
       </c>
       <c r="B26" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3511,16 +3498,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3537,22 +3524,23 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
+          <t>Stenbrobäcken, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560982</v>
+        <v>560588</v>
       </c>
       <c r="R26" t="n">
-        <v>6626056</v>
+        <v>6626447</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3576,27 +3564,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Meståg</t>
+          <t>Skrämdes upp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3611,56 +3599,56 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>63965832</v>
+        <v>63965825</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3715,6 +3703,11 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Meståg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3741,7 +3734,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112973777</v>
+        <v>63965832</v>
       </c>
       <c r="B28" t="n">
         <v>58114</v>
@@ -3771,30 +3764,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Liarsbo, Ramnäs sn, Vstm</t>
+          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560865</v>
+        <v>560982</v>
       </c>
       <c r="R28" t="n">
-        <v>6626044</v>
+        <v>6626056</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3818,27 +3810,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Födosökte i björkar. Lockade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3853,65 +3840,72 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127436291</v>
+        <v>112973777</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Lilla Liarsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560451</v>
+        <v>560865</v>
       </c>
       <c r="R29" t="n">
-        <v>6626509</v>
+        <v>6626044</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3935,12 +3929,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Födosökte i björkar. Lockade</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3951,32 +3960,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127436302</v>
+        <v>127436291</v>
       </c>
       <c r="B30" t="n">
         <v>5199</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560192</v>
+        <v>560451</v>
       </c>
       <c r="R30" t="n">
-        <v>6626228</v>
+        <v>6626509</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127436299</v>
+        <v>127436302</v>
       </c>
       <c r="B31" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560198</v>
+        <v>560192</v>
       </c>
       <c r="R31" t="n">
-        <v>6626344</v>
+        <v>6626228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117962945</v>
+        <v>127436299</v>
       </c>
       <c r="B32" t="n">
-        <v>99153</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4209,53 +4209,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Usträngsbo, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560300</v>
+        <v>560198</v>
       </c>
       <c r="R32" t="n">
-        <v>6626366</v>
+        <v>6626344</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4279,27 +4268,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,29 +4282,37 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127436289</v>
+        <v>117962945</v>
       </c>
       <c r="B33" t="n">
-        <v>106243</v>
+        <v>99153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4338,42 +4320,53 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Usträngsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560581</v>
+        <v>560300</v>
       </c>
       <c r="R33" t="n">
-        <v>6626354</v>
+        <v>6626366</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4397,12 +4390,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4411,37 +4419,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Mikael Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>73168237</v>
+        <v>127436289</v>
       </c>
       <c r="B34" t="n">
-        <v>97986</v>
+        <v>106243</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4449,38 +4449,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560502</v>
+        <v>560581</v>
       </c>
       <c r="R34" t="n">
-        <v>6626399</v>
+        <v>6626354</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4507,12 +4508,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4521,81 +4522,79 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1754023</v>
+        <v>73168237</v>
       </c>
       <c r="B35" t="n">
-        <v>93235</v>
+        <v>97986</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Liarsbo 1 km  NO, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562234</v>
+        <v>560502</v>
       </c>
       <c r="R35" t="n">
-        <v>6626125</v>
+        <v>6626399</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4619,17 +4618,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Antal substrat motsvarar antal mycel, Småkuperat hällmarksområde m fuktiga partier</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,38 +4632,31 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Tallhällmark 90+</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>3 substratenheter # Morän</t>
+          <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Niclas Bergius</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1754224</v>
+        <v>1754023</v>
       </c>
       <c r="B36" t="n">
         <v>93235</v>
@@ -4699,7 +4686,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4709,14 +4696,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Liarsbo 1 km NO, Vstm</t>
+          <t>Stora Liarsbo 1 km  NO, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562346</v>
+        <v>562234</v>
       </c>
       <c r="R36" t="n">
-        <v>6626038</v>
+        <v>6626125</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4753,7 +4740,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
+          <t>Antal substrat motsvarar antal mycel, Småkuperat hällmarksområde m fuktiga partier</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4767,15 +4754,15 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallhällmark 61-90</t>
+          <t>Tallhällmark 90+</t>
         </is>
       </c>
       <c r="AN36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>4 substratenheter # Morän</t>
+          <t>3 substratenheter # Morän</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4793,72 +4780,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130130734</v>
+        <v>1754224</v>
       </c>
       <c r="B37" t="n">
-        <v>57162</v>
+        <v>93235</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+          <t>Stora Liarsbo 1 km NO, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562200</v>
+        <v>562346</v>
       </c>
       <c r="R37" t="n">
-        <v>6625910</v>
+        <v>6626038</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4882,12 +4854,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2006-10-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4898,81 +4875,98 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Tallhällmark 61-90</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>4 substratenheter # Morän</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Niclas Bergius</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115730289</v>
+        <v>130130734</v>
       </c>
       <c r="B38" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562132</v>
+        <v>562200</v>
       </c>
       <c r="R38" t="n">
-        <v>6625955</v>
+        <v>6625910</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5002,24 +4996,9 @@
           <t>2024-04-03</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5034,12 +5013,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5050,54 +5029,61 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125262304</v>
+        <v>115730289</v>
       </c>
       <c r="B39" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brudmossen, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561795</v>
+        <v>562132</v>
       </c>
       <c r="R39" t="n">
-        <v>6626184</v>
+        <v>6625955</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5124,22 +5110,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5148,27 +5139,147 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Hällmarksbarrskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125262304</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brudmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>561795</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6626184</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125286010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/175970</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436279</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1274,6 +1299,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436287</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436288</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1534,6 +1569,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436292</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1664,6 +1704,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436295</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1777,6 +1822,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436303</t>
         </is>
       </c>
     </row>
@@ -1890,6 +1940,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78789447</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1995,6 +2050,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73168242</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2100,6 +2160,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73168257</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2205,6 +2270,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73168331</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2315,6 +2385,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17010077</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2425,6 +2500,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73168294</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2540,6 +2620,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436284</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2655,6 +2740,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436286</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2783,6 +2873,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436294</t>
         </is>
       </c>
     </row>
@@ -2896,6 +2991,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135426956</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3001,6 +3101,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73168318</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3106,6 +3211,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73168344</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3234,6 +3344,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122670754</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3360,6 +3475,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436297</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3484,6 +3604,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122671099</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3608,6 +3733,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125529268</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3731,6 +3861,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63965825</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3849,6 +3984,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63965832</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3973,6 +4113,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112973777</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4084,6 +4229,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436291</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4195,6 +4345,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436302</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4306,6 +4461,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436299</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4435,6 +4595,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117962945</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4544,6 +4709,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436289</t>
         </is>
       </c>
     </row>
@@ -4653,6 +4823,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73168237</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4777,6 +4952,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1754023</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4901,6 +5081,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1754224</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5026,6 +5211,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130734</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5156,6 +5346,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115730289</t>
         </is>
       </c>
     </row>
@@ -5280,8 +5475,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125262304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -2886,7 +2886,7 @@
         <v>135426956</v>
       </c>
       <c r="B20" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -2886,7 +2886,7 @@
         <v>135426956</v>
       </c>
       <c r="B20" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,47 +2883,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73168318</v>
+        <v>135426956</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
+        <v>92011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Altarberget, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560277</v>
+        <v>560118</v>
       </c>
       <c r="R20" t="n">
-        <v>6626496</v>
+        <v>6626316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2950,12 +2951,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2973,6 +2974,11 @@
           <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2987,13 +2993,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73168318</t>
+          <t>https://artportalen.se/Sighting/135426956</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>73168344</v>
+        <v>73168318</v>
       </c>
       <c r="B21" t="n">
         <v>93235</v>
@@ -3030,10 +3036,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560244</v>
+        <v>560277</v>
       </c>
       <c r="R21" t="n">
-        <v>6626458</v>
+        <v>6626496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3097,67 +3103,53 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73168344</t>
+          <t>https://artportalen.se/Sighting/73168318</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122670754</v>
+        <v>73168344</v>
       </c>
       <c r="B22" t="n">
-        <v>57141</v>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560320</v>
+        <v>560244</v>
       </c>
       <c r="R22" t="n">
-        <v>6626329</v>
+        <v>6626458</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3184,27 +3176,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Plockat grus på vägkanten och i rotvälta</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3213,33 +3190,39 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av hällmarker</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122670754</t>
+          <t>https://artportalen.se/Sighting/73168344</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127436297</v>
+        <v>122670754</v>
       </c>
       <c r="B23" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3247,39 +3230,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Stenramsvägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560125</v>
+        <v>560320</v>
       </c>
       <c r="R23" t="n">
-        <v>6626323</v>
+        <v>6626329</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3306,12 +3300,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Plockat grus på vägkanten och i rotvälta</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3322,55 +3331,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stående gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127436297</t>
+          <t>https://artportalen.se/Sighting/122670754</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122671099</v>
+        <v>127436297</v>
       </c>
       <c r="B24" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3378,46 +3363,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenbrobäcken, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560565</v>
+        <v>560125</v>
       </c>
       <c r="R24" t="n">
-        <v>6626352</v>
+        <v>6626323</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3444,27 +3422,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Skrämdes från träd. Sedan tidigare känd järpelokal.</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3475,28 +3438,52 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stående gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122671099</t>
+          <t>https://artportalen.se/Sighting/127436297</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125529268</v>
+        <v>122671099</v>
       </c>
       <c r="B25" t="n">
         <v>57132</v>
@@ -3526,14 +3513,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3543,10 +3530,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560588</v>
+        <v>560565</v>
       </c>
       <c r="R25" t="n">
-        <v>6626447</v>
+        <v>6626352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3573,27 +3560,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Skrämdes upp</t>
+          <t>Skrämdes från träd. Sedan tidigare känd järpelokal.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3619,16 +3606,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125529268</t>
+          <t>https://artportalen.se/Sighting/122671099</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>63965825</v>
+        <v>125529268</v>
       </c>
       <c r="B26" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3636,16 +3623,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3662,22 +3649,23 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
+          <t>Stenbrobäcken, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560982</v>
+        <v>560588</v>
       </c>
       <c r="R26" t="n">
-        <v>6626056</v>
+        <v>6626447</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3701,27 +3689,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Meståg</t>
+          <t>Skrämdes upp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3736,61 +3724,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Inger-Marie Carlsen</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63965825</t>
+          <t>https://artportalen.se/Sighting/125529268</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>63965832</v>
+        <v>63965825</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3847,6 +3835,11 @@
           <t>10:50</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Meståg</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3870,13 +3863,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63965832</t>
+          <t>https://artportalen.se/Sighting/63965825</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112973777</v>
+        <v>63965832</v>
       </c>
       <c r="B28" t="n">
         <v>58114</v>
@@ -3906,30 +3899,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilla Liarsbo, Ramnäs sn, Vstm</t>
+          <t>Liarsbo, vägen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560865</v>
+        <v>560982</v>
       </c>
       <c r="R28" t="n">
-        <v>6626044</v>
+        <v>6626056</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3953,27 +3945,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Födosökte i björkar. Lockade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3988,70 +3975,77 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Inger-Marie Carlsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112973777</t>
+          <t>https://artportalen.se/Sighting/63965832</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127436291</v>
+        <v>112973777</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Lilla Liarsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560451</v>
+        <v>560865</v>
       </c>
       <c r="R29" t="n">
-        <v>6626509</v>
+        <v>6626044</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4075,12 +4069,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Födosökte i björkar. Lockade</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4091,37 +4100,28 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127436291</t>
+          <t>https://artportalen.se/Sighting/112973777</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127436302</v>
+        <v>127436291</v>
       </c>
       <c r="B30" t="n">
         <v>5199</v>
@@ -4161,10 +4161,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560192</v>
+        <v>560451</v>
       </c>
       <c r="R30" t="n">
-        <v>6626228</v>
+        <v>6626509</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,16 +4231,16 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127436302</t>
+          <t>https://artportalen.se/Sighting/127436291</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127436299</v>
+        <v>127436302</v>
       </c>
       <c r="B31" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4248,21 +4248,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560198</v>
+        <v>560192</v>
       </c>
       <c r="R31" t="n">
-        <v>6626344</v>
+        <v>6626228</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4347,16 +4347,16 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127436299</t>
+          <t>https://artportalen.se/Sighting/127436302</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117962945</v>
+        <v>127436299</v>
       </c>
       <c r="B32" t="n">
-        <v>99153</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4364,53 +4364,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Usträngsbo, Ramnäs sn, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560300</v>
+        <v>560198</v>
       </c>
       <c r="R32" t="n">
-        <v>6626366</v>
+        <v>6626344</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4434,27 +4423,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4463,34 +4437,42 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammal barrskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mikael Larsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117962945</t>
+          <t>https://artportalen.se/Sighting/127436299</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127436289</v>
+        <v>117962945</v>
       </c>
       <c r="B33" t="n">
-        <v>106243</v>
+        <v>99153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4498,42 +4480,53 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Altarberget, Usträngsbo, Vstm</t>
+          <t>Usträngsbo, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560581</v>
+        <v>560300</v>
       </c>
       <c r="R33" t="n">
-        <v>6626354</v>
+        <v>6626366</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4557,12 +4550,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fanns efter vägen mellan lv 233 och Usträngsbo</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4571,42 +4579,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Gammal barrskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Mikael Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127436289</t>
+          <t>https://artportalen.se/Sighting/117962945</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>73168237</v>
+        <v>127436289</v>
       </c>
       <c r="B34" t="n">
-        <v>97986</v>
+        <v>106243</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4614,38 +4614,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stenbromossen SV, Vstm</t>
+          <t>Altarberget, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560502</v>
+        <v>560581</v>
       </c>
       <c r="R34" t="n">
-        <v>6626399</v>
+        <v>6626354</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4672,12 +4673,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4686,86 +4687,84 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av hällmarker</t>
+          <t>Gammal barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73168237</t>
+          <t>https://artportalen.se/Sighting/127436289</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1754023</v>
+        <v>73168237</v>
       </c>
       <c r="B35" t="n">
-        <v>93235</v>
+        <v>97986</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Liarsbo 1 km  NO, Vstm</t>
+          <t>Stenbromossen SV, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562234</v>
+        <v>560502</v>
       </c>
       <c r="R35" t="n">
-        <v>6626125</v>
+        <v>6626399</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4789,17 +4788,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2006-10-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Antal substrat motsvarar antal mycel, Småkuperat hällmarksområde m fuktiga partier</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4808,43 +4802,36 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Tallhällmark 90+</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>3 substratenheter # Morän</t>
+          <t>Barrblandskog, inslag av hällmarker</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Niclas Bergius</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1754023</t>
+          <t>https://artportalen.se/Sighting/73168237</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1754224</v>
+        <v>1754023</v>
       </c>
       <c r="B36" t="n">
         <v>93235</v>
@@ -4874,7 +4861,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4884,14 +4871,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Liarsbo 1 km NO, Vstm</t>
+          <t>Stora Liarsbo 1 km  NO, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562346</v>
+        <v>562234</v>
       </c>
       <c r="R36" t="n">
-        <v>6626038</v>
+        <v>6626125</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4928,7 +4915,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
+          <t>Antal substrat motsvarar antal mycel, Småkuperat hällmarksområde m fuktiga partier</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4942,15 +4929,15 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Tallhällmark 61-90</t>
+          <t>Tallhällmark 90+</t>
         </is>
       </c>
       <c r="AN36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>4 substratenheter # Morän</t>
+          <t>3 substratenheter # Morän</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4967,78 +4954,63 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1754224</t>
+          <t>https://artportalen.se/Sighting/1754023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130130734</v>
+        <v>1754224</v>
       </c>
       <c r="B37" t="n">
-        <v>57162</v>
+        <v>93235</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+          <t>Stora Liarsbo 1 km NO, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562200</v>
+        <v>562346</v>
       </c>
       <c r="R37" t="n">
-        <v>6625910</v>
+        <v>6626038</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5062,12 +5034,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2006-10-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2006-10-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Antal substrat motsvarar antal mycel, Större hällmark ned mot mosstallskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5078,86 +5055,103 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Tallhällmark 61-90</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>4 substratenheter # Morän</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Niclas Bergius</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130130734</t>
+          <t>https://artportalen.se/Sighting/1754224</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115730289</v>
+        <v>130130734</v>
       </c>
       <c r="B38" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562132</v>
+        <v>562200</v>
       </c>
       <c r="R38" t="n">
-        <v>6625955</v>
+        <v>6625910</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5187,24 +5181,9 @@
           <t>2024-04-03</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5219,12 +5198,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5234,60 +5213,67 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115730289</t>
+          <t>https://artportalen.se/Sighting/130130734</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125262304</v>
+        <v>115730289</v>
       </c>
       <c r="B39" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brudmossen, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561795</v>
+        <v>562132</v>
       </c>
       <c r="R39" t="n">
-        <v>6626184</v>
+        <v>6625955</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5314,22 +5300,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lämplig häckmiljö med en mosse med enstaka lövträd i kanten</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5338,28 +5329,153 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Hällmarksbarrskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115730289</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125262304</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brudmossen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>561795</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6626184</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125262304</t>
         </is>
@@ -5405,6 +5521,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -2886,7 +2886,7 @@
         <v>135426956</v>
       </c>
       <c r="B20" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21560-2025 artfynd.xlsx
+++ b/artfynd/A 21560-2025 artfynd.xlsx
@@ -2886,7 +2886,7 @@
         <v>135426956</v>
       </c>
       <c r="B20" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
